--- a/survey_templates/022_medical_innovation_awareness_survey--survey_templates.xlsx
+++ b/survey_templates/022_medical_innovation_awareness_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,13 +525,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>What is a New Medical Innovation?</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is a new medical innovation?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please provide your understanding of what a new medical innovation is.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -543,41 +547,49 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>awareness_sources_1</t>
+          <t>information_sources</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Which of the following best describes where you learn about new medical innovations?</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Which of the following sources do you often get information on new medical innovations?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>List the sources you often get information from.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>familiarity_level_1</t>
+          <t>familiarity_level</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>How familiar are you with the following medical innovations?</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>How familiar are you with new medical innovations?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Describe your level of familiarity with new medical innovations.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -589,7 +601,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>attitudes_towards_innovation_1</t>
+          <t>attitudes_towards_innovation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -597,102 +609,122 @@
           <t>What is your attitude towards adopting new medical innovations?</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Check all that apply.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>information_sources_1</t>
+          <t>survey_questions_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>From which of the following sources do you often get information on new medical innovations?</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>What is your understanding of AI in medical innovations?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Provide your understanding of AI in medical innovations.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>attitudes_towards_innovation_2</t>
+          <t>familiarity_level_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What is your attitude towards adopting new medical innovations?</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>How familiar are you with AI in medical innovations?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Describe your level of familiarity with AI in medical innovations.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>information_sources_2</t>
+          <t>survey_questions_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>From which of the following sources do you often get information on new medical innovations?</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>What is your understanding of Gene Therapy in medical innovations?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Provide your understanding of Gene Therapy in medical innovations.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>attitudes_towards_innovation_3</t>
+          <t>familiarity_level_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What is your attitude towards adopting new medical innovations?</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>How familiar are you with Gene Therapy in medical innovations?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Describe your level of familiarity with Gene Therapy in medical innovations.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -704,18 +736,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>familiarity_level_2</t>
+          <t>survey_questions_4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>How familiar are you with new medical innovations?</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>What is your understanding of Blockchain in medical innovations?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Provide your understanding of Blockchain in medical innovations.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -727,15 +763,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>survey_questions_1</t>
+          <t>familiarity_level_4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>What is your understanding of AI in medical innovations?</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>How familiar are you with Blockchain in medical innovations?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Describe your level of familiarity with Blockchain in medical innovations.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -750,15 +790,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>familiarity_level_3</t>
+          <t>survey_questions_5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>How familiar are you with Blockchain in medical innovations?</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>What is your understanding of Robotics in medical innovations?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Provide your understanding of Robotics in medical innovations.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -773,15 +817,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>familiarity_level_4</t>
+          <t>familiarity_level_5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>How familiar are you with Gene Therapy in medical innovations?</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>How familiar are you with Robotics in medical innovations?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Describe your level of familiarity with Robotics in medical innovations.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -791,20 +839,24 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>attitudes_towards_innovation_4</t>
+          <t>survey_questions_6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>What is your attitude towards adopting new medical innovations?</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Survey Questions 6</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Provide your understanding of Robotics in medical innovations.</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -819,7 +871,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>information_sources_3</t>
+          <t>information_sources_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -827,7 +879,11 @@
           <t>From which of the following sources do you often get information on new medical innovations?</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>List the sources you often get information from.</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
@@ -842,15 +898,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>attitudes_towards_innovation_5</t>
+          <t>attitudes_towards_innovation_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>What is your attitude towards adopting new medical innovations?</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Attitudes Towards Innovation 2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Check all that apply.</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -865,15 +925,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>survey_questions_2</t>
+          <t>survey_questions_7</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>What is your understanding of Blockchain in medical innovations?</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Survey Questions 7</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Provide your understanding of AI in medical innovations.</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -883,20 +947,24 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>attitudes_towards_innovation_6</t>
+          <t>familiarity_level_6</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>What is your attitude towards adopting new medical innovations?</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Familiarity Level 6</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Describe your level of familiarity with AI in medical innovations.</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
@@ -906,20 +974,24 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>information_sources_4</t>
+          <t>survey_questions_8</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>From which of the following sources do you often get information on new medical innovations?</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Survey Questions 8</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Provide your understanding of Gene Therapy in medical innovations.</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>no</t>
@@ -929,20 +1001,24 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>familiarity_level_5</t>
+          <t>information_sources_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>How familiar are you with Gene Therapy in medical innovations?</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>Information Sources 3</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>List the sources you often get information from.</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>no</t>
@@ -952,136 +1028,25 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>survey_questions_3</t>
+          <t>attitudes_towards_innovation_3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>What is your understanding of Robotics in medical innovations?</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>Attitudes Towards Innovation 3</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Check all that apply.</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>attitudes_towards_innovation_7</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>What is your attitude towards adopting new medical innovations?</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>information_sources_5</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>From which of the following sources do you often get information on new medical innovations?</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>familiarity_level_6</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>How familiar are you with new medical innovations?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>attitudes_towards_innovation_8</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>What is your attitude towards adopting new medical innovations?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>survey_questions_4</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>What is your understanding of Gene Therapy in medical innovations?</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,7 +1063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1126,916 +1091,355 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>awareness_sources_1_choices</t>
+          <t>information_sources_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>twitter</t>
+          <t>google</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Twitter</t>
+          <t>Google</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>awareness_sources_1_choices</t>
+          <t>information_sources_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>podcasts</t>
+          <t>online_forums</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Podcasts</t>
+          <t>Online Forums</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>awareness_sources_1_choices</t>
+          <t>information_sources_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>social_media</t>
+          <t>offline_conferences</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Social Media</t>
+          <t>Offline Conferences</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>awareness_sources_1_choices</t>
+          <t>information_sources_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>online_news</t>
+          <t>print_books</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Online News</t>
+          <t>Print Books</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>awareness_sources_1_choices</t>
+          <t>attitudes_towards_innovation_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>offline_sources</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Offline Sources</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>awareness_sources_1_choices</t>
+          <t>attitudes_towards_innovation_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>print_magazines</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Print Magazines</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>familiarity_level_1_choices</t>
+          <t>attitudes_towards_innovation_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>familiarity_level_1_choices</t>
+          <t>information_sources_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>blockchain</t>
+          <t>google</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Blockchain</t>
+          <t>Google</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>familiarity_level_1_choices</t>
+          <t>information_sources_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>gene_therapy</t>
+          <t>online_forums</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Gene Therapy</t>
+          <t>Online Forums</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>familiarity_level_1_choices</t>
+          <t>information_sources_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>robotics</t>
+          <t>offline_conferences</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Robotics</t>
+          <t>Offline Conferences</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>attitudes_towards_innovation_1_choices</t>
+          <t>information_sources_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>print_books</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Print Books</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>attitudes_towards_innovation_1_choices</t>
+          <t>attitudes_towards_innovation_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>attitudes_towards_innovation_1_choices</t>
+          <t>attitudes_towards_innovation_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>information_sources_1_choices</t>
+          <t>attitudes_towards_innovation_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>information_sources_1_choices</t>
+          <t>information_sources_3_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>online_forums</t>
+          <t>google</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Online Forums</t>
+          <t>Google</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>information_sources_1_choices</t>
+          <t>information_sources_3_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>offline_conferences</t>
+          <t>online_forums</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Offline Conferences</t>
+          <t>Online Forums</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>information_sources_1_choices</t>
+          <t>information_sources_3_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>print_books</t>
+          <t>offline_conferences</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Print Books</t>
+          <t>Offline Conferences</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>attitudes_towards_innovation_2_choices</t>
+          <t>information_sources_3_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>print_books</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Print Books</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>attitudes_towards_innovation_2_choices</t>
+          <t>attitudes_towards_innovation_3_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>attitudes_towards_innovation_2_choices</t>
+          <t>attitudes_towards_innovation_3_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>information_sources_2_choices</t>
+          <t>attitudes_towards_innovation_3_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>information_sources_2_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>offline_conferences</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Offline Conferences</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>information_sources_2_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>online_forums</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Online Forums</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>information_sources_2_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>print_books</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Print Books</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>attitudes_towards_innovation_3_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>attitudes_towards_innovation_3_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>attitudes_towards_innovation_3_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>negative</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>attitudes_towards_innovation_4_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>attitudes_towards_innovation_4_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>attitudes_towards_innovation_4_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>negative</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>information_sources_3_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>google</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>information_sources_3_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>online_forums</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Online Forums</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>information_sources_3_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>offline_conferences</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Offline Conferences</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>information_sources_3_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>print_books</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Print Books</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>attitudes_towards_innovation_5_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>attitudes_towards_innovation_5_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>attitudes_towards_innovation_5_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>negative</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>attitudes_towards_innovation_6_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>attitudes_towards_innovation_6_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>attitudes_towards_innovation_6_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>negative</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>information_sources_4_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>google</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>information_sources_4_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>online_forums</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Online Forums</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>information_sources_4_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>offline_conferences</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Offline Conferences</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>information_sources_4_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>print_books</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Print Books</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>attitudes_towards_innovation_7_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>attitudes_towards_innovation_7_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>attitudes_towards_innovation_7_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>negative</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>information_sources_5_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>google</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>information_sources_5_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>online_forums</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Online Forums</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>information_sources_5_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>offline_conferences</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Offline Conferences</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>information_sources_5_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>print_books</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Print Books</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>attitudes_towards_innovation_8_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>attitudes_towards_innovation_8_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>attitudes_towards_innovation_8_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>negative</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
